--- a/artfynd/A 29381-2025 artfynd.xlsx
+++ b/artfynd/A 29381-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>104073846</v>
       </c>
       <c r="B3" t="n">
-        <v>57833</v>
+        <v>57834</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29381-2025 artfynd.xlsx
+++ b/artfynd/A 29381-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>104073846</v>
       </c>
       <c r="B3" t="n">
-        <v>57834</v>
+        <v>57838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29381-2025 artfynd.xlsx
+++ b/artfynd/A 29381-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>104073793</v>
       </c>
       <c r="B2" t="n">
-        <v>56311</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>843853.3145742696</v>
+        <v>843853</v>
       </c>
       <c r="R2" t="n">
-        <v>7319782.321438108</v>
+        <v>7319782</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,19 +751,9 @@
           <t>2022-06-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,11 +783,11 @@
         <v>104073846</v>
       </c>
       <c r="B3" t="n">
-        <v>57838</v>
+        <v>57860</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -889,6 +874,103 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>104073791</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100110</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gråspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picus canus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bläsberget, myr söder Jämtön, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>843853</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7319782</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-06-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-06-05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo, Åke Svensson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29381-2025 artfynd.xlsx
+++ b/artfynd/A 29381-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104073793</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104073846</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,8 +986,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104073791</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>